--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -8,12 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座 销控表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -116,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -181,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,54 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -766,7 +619,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-01-21</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -862,7 +715,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-13</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -908,7 +761,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -954,7 +807,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-10</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1000,7 +853,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-03</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1046,7 +899,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-05-01</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1092,7 +945,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-01-24</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1138,7 +991,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-01-24</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1184,7 +1037,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-01-09</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1230,7 +1083,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-01-09</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1276,7 +1129,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-08-20</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1322,7 +1175,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-03</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1368,7 +1221,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-04-16</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1414,7 +1267,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-05-16</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1460,7 +1313,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-05-10</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1506,7 +1359,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1552,7 +1405,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-04-25</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1648,7 +1501,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-04-22</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1694,7 +1547,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-03-20</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1790,7 +1643,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-30</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1982,7 +1835,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2078,7 +1931,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-10-28</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2174,7 +2027,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2270,7 +2123,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-04-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2316,7 +2169,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2362,7 +2215,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2408,7 +2261,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-01-29</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2454,7 +2307,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-01-28</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2500,7 +2353,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-08</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2546,7 +2399,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-01-31</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2592,7 +2445,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-08</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2638,7 +2491,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-05-23</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2684,7 +2537,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-04-16</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2830,7 +2683,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-06-19</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2876,7 +2729,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-29</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3022,7 +2875,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-04</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3118,7 +2971,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-04</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3614,7 +3467,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4906,7 +4759,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4952,7 +4805,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4998,7 +4851,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -5044,7 +4897,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5090,7 +4943,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-07</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -5136,7 +4989,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-10-24</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5182,7 +5035,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5228,7 +5081,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5274,7 +5127,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-02</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5320,7 +5173,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5366,7 +5219,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-16</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5412,7 +5265,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5458,7 +5311,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5504,7 +5357,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-04-14</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5550,7 +5403,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-07-04</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5596,7 +5449,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-21</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5642,7 +5495,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-07-10</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5688,7 +5541,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-10-15</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5734,7 +5587,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-14</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5826,7 +5679,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5872,7 +5725,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5918,7 +5771,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5964,7 +5817,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -6056,7 +5909,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -6102,7 +5955,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -6148,7 +6001,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-04-11</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -6194,7 +6047,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-04-22</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6286,7 +6139,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6332,7 +6185,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6378,7 +6231,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6424,7 +6277,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6470,7 +6323,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6516,7 +6369,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6562,7 +6415,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -6608,7 +6461,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6654,7 +6507,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6700,7 +6553,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-02-14</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6746,7 +6599,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-01-06</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6792,7 +6645,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-04-10</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6884,7 +6737,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6976,7 +6829,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -7114,7 +6967,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-08-27</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -7160,7 +7013,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7206,7 +7059,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7252,7 +7105,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-09-02</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7344,7 +7197,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7390,7 +7243,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7436,7 +7289,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7482,7 +7335,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7528,7 +7381,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7574,7 +7427,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -7620,7 +7473,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7666,7 +7519,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7712,7 +7565,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-12</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7758,7 +7611,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7804,7 +7657,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7850,7 +7703,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7896,7 +7749,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7942,7 +7795,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7988,7 +7841,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -8034,7 +7887,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -8080,7 +7933,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -8126,7 +7979,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -8172,7 +8025,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8218,7 +8071,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-12-13</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8264,7 +8117,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-02</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8310,7 +8163,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8356,7 +8209,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8402,7 +8255,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-12</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8448,7 +8301,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8494,7 +8347,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8540,7 +8393,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-27</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8586,7 +8439,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8632,7 +8485,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8678,7 +8531,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-29</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8724,7 +8577,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8770,7 +8623,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-02</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -8816,7 +8669,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8862,7 +8715,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8908,7 +8761,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8954,7 +8807,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -9000,7 +8853,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -9046,7 +8899,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -9092,7 +8945,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-15</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -9138,7 +8991,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-08-05</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -9184,7 +9037,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9230,7 +9083,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9276,7 +9129,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9822,7 +9675,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9868,7 +9721,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -10014,7 +9867,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -10110,7 +9963,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -10156,7 +10009,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -10202,7 +10055,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10248,7 +10101,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10294,7 +10147,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -10340,7 +10193,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10386,7 +10239,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10432,7 +10285,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10478,7 +10331,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10524,7 +10377,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10620,7 +10473,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10716,7 +10569,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -17786,4264 +17639,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>24 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2086呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 2031呎 (4+房)
-$15,304万
-$75,350/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1585呎 (4+房)
-$10,355万
-$65,330/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1585呎 (4+房)
-$9,780万
-$61,703/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-$6,745万
-$57,500/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1585呎 (4+房)
-$8,927万
-$56,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-$6,629万
-$56,513/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1585呎 (4+房)
-$10,285万
-$64,887/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-$7,217万
-$61,527/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1585呎 (4+房)
-$8,981万
-$56,660/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-$6,873万
-$58,597/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1585呎 (4+房)
-$8,876万
-$56,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-$6,228万
-$55,164/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1540呎 (4+房)
-$9,935万
-$64,513/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-$6,389万
-$54,465/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1540呎 (4+房)
-$8,198万
-$53,235/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-$6,690万
-$57,033/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1585呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-$6,104万
-$52,036/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1585呎 (4+房)
-$8,000万
-$50,473/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-$5,706万
-$48,642/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1524呎 (4+房)
-$8,389万
-$55,045/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 1119呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2373呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 2373呎 (4+房)
-$20,000万
-$84,282/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-$10,900万
-$70,096/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-$10,237万
-$64,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1555呎 (4+房)
-$10,006万
-$64,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-$10,529万
-$65,846/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-$9,198万
-$57,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1423呎 (4+房)
-$7,852万
-$55,181/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-$9,513万
-$59,493/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-$8,274万
-$56,403/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-$950万
-$5,940/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1423呎 (4+房)
-$7,628万
-$53,608/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-$9,596万
-$60,010/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1423呎 (4+房)
-$1,429万
-$10,042/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-$8,000万
-$54,533/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-$8,319万
-$52,024/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-$6,904万
-$47,061/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1599呎 (4+房)
-$7,391万
-$46,224/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 1467呎 (4+房)
-招标单位
--
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1485呎 (4+房)
-$9,848万
-$66,320/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1402呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>32 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>30 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2074呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2023呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-$5,939万
-$40,789/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 1499呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 1173呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 1499呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 1499呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1456呎 (4+房)
-$7,391万
-$50,764/呎
-(18年-06月)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 1129呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 1434呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 1119呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 - 5A座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>99 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>88 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>A | 764呎 (2房)
-$4,360万
-$57,075/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,768万
-$48,582/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 718呎 (2房)
-$3,920万
-$54,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,329万
-$34,977/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,285万
-$34,837/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,083万
-$37,863/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,544万
-$42,407/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,848万
-$48,893/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,333万
-$44,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,321万
-$34,751/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,277万
-$34,612/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,076万
-$37,620/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,605万
-$44,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,714万
-$45,343/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,391万
-$45,629/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,366万
-$35,938/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,341万
-$36,331/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,091万
-$38,146/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,528万
-$41,988/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,656万
-$43,811/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,310万
-$44,086/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,339万
-$35,235/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,599万
-$43,325/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,091万
-$38,146/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,942万
-$53,360/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,680万
-$44,456/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,344万
-$44,735/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,300万
-$34,203/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,257万
-$34,066/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,307万
-$45,713/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,488万
-$40,878/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,781万
-$47,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$1,980万
-$37,786/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$1,320万
-$34,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,410万
-$38,221/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,075万
-$37,600/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,551万
-$42,623/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,657万
-$43,840/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,312万
-$44,115/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$1,424万
-$37,571/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,477万
-$40,031/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,050万
-$36,713/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,938万
-$53,250/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$2,071万
-$54,788/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,340万
-$44,655/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$1,682万
-$44,375/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,456万
-$39,453/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,331万
-$46,535/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,457万
-$40,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,949万
-$51,569/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,202万
-$42,032/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,306万
-$34,367/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,263万
-$34,231/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,176万
-$41,110/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,447万
-$39,750/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,568万
-$41,479/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,187万
-$41,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,277万
-$33,611/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,235万
-$33,476/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,041万
-$36,385/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,437万
-$39,472/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,557万
-$41,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,172万
-$41,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,376万
-$36,216/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,232万
-$33,390/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,038万
-$36,294/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,437万
-$39,472/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,557万
-$41,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,172万
-$41,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,408万
-$37,043/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,232万
-$33,390/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,038万
-$36,294/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,445万
-$39,699/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,566万
-$41,424/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,141万
-$40,865/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$1,293万
-$34,116/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,250万
-$33,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,053万
-$36,835/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,435万
-$39,418/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,680万
-$44,433/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,169万
-$41,392/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,290万
-$33,939/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,285万
-$34,819/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,051万
-$36,742/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,512万
-$41,541/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,517万
-$40,125/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,116万
-$40,378/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,261万
-$33,191/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,220万
-$33,059/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,028万
-$35,934/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 364呎 (1房)
-$1,393万
-$38,261/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 378呎 (1房)
-$1,509万
-$39,926/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 524呎 (2房)
-$2,105万
-$40,175/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 380呎 (1房)
-$1,258万
-$33,110/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="18" t="inlineStr">
-        <is>
-          <t>E | 369呎 (1房)
-$1,217万
-$32,975/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="18" t="inlineStr">
-        <is>
-          <t>F | 286呎 (开放式)
-$1,025万
-$35,841/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>32 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 2371呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 2371呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 1602呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 1602呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 1602呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 1602呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1559呎 (4+房)
-$8,141万
-$52,217/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1446呎 (4+房)
-$6,827万
-$47,213/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 1602呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 1602呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1446呎 (4+房)
-$6,607万
-$45,690/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1559呎 (4+房)
-$8,099万
-$51,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1446呎 (4+房)
-$6,496万
-$44,926/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1559呎 (4+房)
-$8,619万
-$55,284/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1446呎 (4+房)
-$6,386万
-$44,163/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1559呎 (4+房)
-$7,209万
-$46,241/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1446呎 (4+房)
-$6,279万
-$43,426/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1559呎 (4+房)
-$7,017万
-$45,008/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1446呎 (4+房)
-$6,173万
-$42,690/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1559呎 (4+房)
-$6,825万
-$43,775/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1446呎 (4+房)
-$6,072万
-$41,990/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1559呎 (4+房)
-$6,632万
-$42,542/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 1559呎 (4+房)
-$6,472万
-$41,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 1602呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 1424呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 - 6座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>140 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>13 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>127 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>A | 1063呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>B | 813呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 1063呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 813呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-$1,682万
-$44,160/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-$1,678万
-$44,052/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-$1,622万
-$44,934/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-$1,623万
-$44,344/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-$1,668万
-$44,833/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 603呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-$1,674万
-$43,942/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-$1,618万
-$44,823/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-$1,619万
-$44,235/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-$1,664万
-$44,723/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 581呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>B | 529呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 458呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>E | 381呎 (1房)
-$1,670万
-$43,832/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>F | 361呎 (1房)
-$1,614万
-$44,709/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>G | 366呎 (1房)
-$1,615万
-$44,123/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
-        <is>
-          <t>H | 372呎 (1房)
-$1,660万
-$44,610/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -8,6 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5A座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6座" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +25,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +47,107 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +158,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +239,66 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +675,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -17639,4 +17840,4264 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2086呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2031呎 (4+房)
+$15304万
+$75,350/呎
+(20年-01月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1585呎 (4+房)
+$10355万
+$65,330/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1585呎 (4+房)
+$9780万
+$61,703/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+$6745万
+$57,500/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1585呎 (4+房)
+$8927万
+$56,324/呎
+(18年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+$6629万
+$56,513/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1585呎 (4+房)
+$10285万
+$64,887/呎
+(18年-01月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+$7217万
+$61,527/呎
+(18年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1585呎 (4+房)
+$8981万
+$56,660/呎
+(18年-01月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+$6873万
+$58,597/呎
+(18年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1585呎 (4+房)
+$8876万
+$56,000/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+$6228万
+$55,164/呎
+(19年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1540呎 (4+房)
+$9935万
+$64,513/呎
+(18年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+$6389万
+$54,465/呎
+(18年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1540呎 (4+房)
+$8198万
+$53,235/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+$6690万
+$57,033/呎
+(18年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1585呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+$6104万
+$52,036/呎
+(18年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1585呎 (4+房)
+$8000万
+$50,473/呎
+(19年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+$5706万
+$48,642/呎
+(18年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1524呎 (4+房)
+$8389万
+$55,045/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 1119呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2373呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2373呎 (4+房)
+$20000万
+$84,282/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+$10900万
+$70,096/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+$10237万
+$64,024/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1555呎 (4+房)
+$10006万
+$64,344/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+$10529万
+$65,846/呎
+(18年-04月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+$9198万
+$57,523/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1423呎 (4+房)
+$7852万
+$55,181/呎
+(18年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+$9513万
+$59,493/呎
+(18年-01月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+$8274万
+$56,403/呎
+(18年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+$950万
+$5,940/呎
+(18年-01月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1423呎 (4+房)
+$7628万
+$53,608/呎
+(21年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+$9596万
+$60,010/呎
+(18年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1423呎 (4+房)
+$1429万
+$10,042/呎
+(19年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+$8000万
+$54,533/呎
+(18年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+$8319万
+$52,024/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+$6904万
+$47,061/呎
+(19年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1599呎 (4+房)
+$7391万
+$46,224/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 1467呎 (4+房)
+招标单位
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1485呎 (4+房)
+$9848万
+$66,320/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1402呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>A | 2074呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>A | 2023呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+$5939万
+$40,789/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 1499呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>B | 1173呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>A | 1499呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 1499呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1456呎 (4+房)
+$7391万
+$50,764/呎
+(18年-06月)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>B | 1129呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>A | 1434呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 1119呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5A座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>A | 764呎 (2房)
+$4360万
+$57,075/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1768万
+$48,582/呎
+(18年-10月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 718呎 (2房)
+$3920万
+$54,596/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1329万
+$34,977/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1285万
+$34,837/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1083万
+$37,863/呎
+(18年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1544万
+$42,407/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1848万
+$48,893/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2333万
+$44,527/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1321万
+$34,751/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1277万
+$34,612/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1076万
+$37,620/呎
+(18年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1605万
+$44,087/呎
+(19年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1714万
+$45,343/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2391万
+$45,629/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1366万
+$35,938/呎
+(19年-07月)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1341万
+$36,331/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1091万
+$38,146/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1528万
+$41,988/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1656万
+$43,811/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2310万
+$44,086/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1339万
+$35,235/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1599万
+$43,325/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1091万
+$38,146/呎
+(20年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1942万
+$53,360/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1680万
+$44,456/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2344万
+$44,735/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1300万
+$34,203/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1257万
+$34,066/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1307万
+$45,713/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1488万
+$40,878/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1781万
+$47,129/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$1980万
+$37,786/呎
+(20年-06月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$1320万
+$34,821/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1410万
+$38,221/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1075万
+$37,600/呎
+(18年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1551万
+$42,623/呎
+(19年-04月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1657万
+$43,840/呎
+(19年-01月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2312万
+$44,115/呎
+(19年-02月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$1424万
+$37,571/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1477万
+$40,031/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1050万
+$36,713/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1938万
+$53,250/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$2071万
+$54,788/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2340万
+$44,655/呎
+(21年-11月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$1682万
+$44,375/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1456万
+$39,453/呎
+(20年-07月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1331万
+$46,535/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1457万
+$40,030/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1949万
+$51,569/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2202万
+$42,032/呎
+(18年-09月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1306万
+$34,367/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1263万
+$34,231/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1176万
+$41,110/呎
+(19年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1447万
+$39,750/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1568万
+$41,479/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2187万
+$41,738/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1277万
+$33,611/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1235万
+$33,476/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1041万
+$36,385/呎
+(18年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1437万
+$39,472/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1557万
+$41,188/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2172万
+$41,446/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1376万
+$36,216/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1232万
+$33,390/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1038万
+$36,294/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1437万
+$39,472/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1557万
+$41,188/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2172万
+$41,446/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1408万
+$37,043/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1232万
+$33,390/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G17" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1038万
+$36,294/呎
+(18年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1445万
+$39,699/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1566万
+$41,424/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2141万
+$40,865/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$1293万
+$34,116/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1250万
+$33,888/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1053万
+$36,835/呎
+(20年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1435万
+$39,418/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1680万
+$44,433/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2169万
+$41,392/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1290万
+$33,939/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1285万
+$34,819/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1051万
+$36,742/呎
+(19年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1512万
+$41,541/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1517万
+$40,125/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2116万
+$40,378/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1261万
+$33,191/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1220万
+$33,059/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1028万
+$35,934/呎
+(18年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 364呎 (1房)
+$1393万
+$38,261/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 378呎 (1房)
+$1509万
+$39,926/呎
+(18年-07月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 524呎 (2房)
+$2105万
+$40,175/呎
+(19年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 380呎 (1房)
+$1258万
+$33,110/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 369呎 (1房)
+$1217万
+$32,975/呎
+(18年-08月)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 286呎 (开放式)
+$1025万
+$35,841/呎
+(18年-07月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>A | 2371呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>A | 2371呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 1602呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 1602呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A | 1602呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>A | 1602呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1559呎 (4+房)
+$8141万
+$52,217/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1446呎 (4+房)
+$6827万
+$47,213/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1602呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 1602呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1446呎 (4+房)
+$6607万
+$45,690/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1559呎 (4+房)
+$8099万
+$51,950/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1446呎 (4+房)
+$6496万
+$44,926/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1559呎 (4+房)
+$8619万
+$55,284/呎
+(23年-12月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1446呎 (4+房)
+$6386万
+$44,163/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1559呎 (4+房)
+$7209万
+$46,241/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1446呎 (4+房)
+$6279万
+$43,426/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1559呎 (4+房)
+$7017万
+$45,008/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1446呎 (4+房)
+$6173万
+$42,690/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1559呎 (4+房)
+$6825万
+$43,775/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1446呎 (4+房)
+$6072万
+$41,990/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1559呎 (4+房)
+$6632万
+$42,542/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 1559呎 (4+房)
+$6472万
+$41,514/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 1602呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 1424呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>6座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>A | 1063呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>B | 813呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>A | 1063呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>B | 813呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+$1682万
+$44,160/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+$1678万
+$44,052/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+$1622万
+$44,934/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H20" s="25" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+$1623万
+$44,344/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+$1668万
+$44,833/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>A | 603呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+$1674万
+$43,942/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+$1618万
+$44,823/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+$1619万
+$44,235/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I21" s="25" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+$1664万
+$44,723/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>A | 581呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>B | 529呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>C | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>D | 458呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>E | 381呎 (1房)
+$1670万
+$43,832/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>F | 361呎 (1房)
+$1614万
+$44,709/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H22" s="25" t="inlineStr">
+        <is>
+          <t>G | 366呎 (1房)
+$1615万
+$44,123/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="inlineStr">
+        <is>
+          <t>H | 372呎 (1房)
+$1660万
+$44,610/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -675,7 +675,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2373</v>
+        <v>2322</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2384,14 +2384,14 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
         <v>200000000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>84282</v>
+        <v>86133</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>200000000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>84282</v>
+        <v>86133</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
           <t>A | 2031呎 (4+房)
 $15304万
 $75,350/呎
-(20年-01月-21日)</t>
+(20年-01月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -24455,7 +24455,7 @@
           <t>A | 1585呎 (4+房)
 $10355万
 $65,330/呎
-(19年-05月-13日)</t>
+(19年-05月)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -24478,7 +24478,7 @@
           <t>A | 1585呎 (4+房)
 $9780万
 $61,703/呎
-(19年-01月-10日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -24486,7 +24486,7 @@
           <t>B | 1173呎 (3房)
 $6745万
 $57,500/呎
-(18年-06月-12日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
           <t>A | 1585呎 (4+房)
 $8927万
 $56,324/呎
-(18年-05月-01日)</t>
+(18年-05月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -24509,7 +24509,7 @@
           <t>B | 1173呎 (3房)
 $6629万
 $56,513/呎
-(18年-06月-03日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -24524,7 +24524,7 @@
           <t>A | 1585呎 (4+房)
 $10285万
 $64,887/呎
-(18年-01月-24日)</t>
+(18年-01月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -24532,7 +24532,7 @@
           <t>B | 1173呎 (3房)
 $7217万
 $61,527/呎
-(18年-01月-24日)</t>
+(18年-01月)</t>
         </is>
       </c>
     </row>
@@ -24547,7 +24547,7 @@
           <t>A | 1585呎 (4+房)
 $8981万
 $56,660/呎
-(18年-01月-09日)</t>
+(18年-01月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24555,7 +24555,7 @@
           <t>B | 1173呎 (3房)
 $6873万
 $58,597/呎
-(18年-01月-09日)</t>
+(18年-01月)</t>
         </is>
       </c>
     </row>
@@ -24570,7 +24570,7 @@
           <t>A | 1585呎 (4+房)
 $8876万
 $56,000/呎
-(19年-01月-03日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -24578,7 +24578,7 @@
           <t>B | 1129呎 (3房)
 $6228万
 $55,164/呎
-(19年-08月-20日)</t>
+(19年-08月)</t>
         </is>
       </c>
     </row>
@@ -24593,7 +24593,7 @@
           <t>A | 1540呎 (4+房)
 $9935万
 $64,513/呎
-(18年-05月-16日)</t>
+(18年-05月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -24601,7 +24601,7 @@
           <t>B | 1173呎 (3房)
 $6389万
 $54,465/呎
-(18年-04月-16日)</t>
+(18年-04月)</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
           <t>A | 1540呎 (4+房)
 $8198万
 $53,235/呎
-(18年-06月-05日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -24624,7 +24624,7 @@
           <t>B | 1173呎 (3房)
 $6690万
 $57,033/呎
-(18年-05月-10日)</t>
+(18年-05月)</t>
         </is>
       </c>
     </row>
@@ -24647,7 +24647,7 @@
           <t>B | 1173呎 (3房)
 $6104万
 $52,036/呎
-(18年-04月-25日)</t>
+(18年-04月)</t>
         </is>
       </c>
     </row>
@@ -24662,7 +24662,7 @@
           <t>A | 1585呎 (4+房)
 $8000万
 $50,473/呎
-(19年-03月-20日)</t>
+(19年-03月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -24670,7 +24670,7 @@
           <t>B | 1173呎 (3房)
 $5706万
 $48,642/呎
-(18年-04月-22日)</t>
+(18年-04月)</t>
         </is>
       </c>
     </row>
@@ -24685,7 +24685,7 @@
           <t>A | 1524呎 (4+房)
 $8389万
 $55,045/呎
-(21年-03月-30日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -24832,10 +24832,10 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 2373呎 (4+房)
+          <t>A | 2322呎 (4+房)
 $20000万
-$84,282/呎
-(26年-07月-01日)</t>
+$86,133/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -24851,7 +24851,7 @@
           <t>A | 1555呎 (4+房)
 $10900万
 $70,096/呎
-(21年-11月-18日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -24874,7 +24874,7 @@
           <t>A | 1599呎 (4+房)
 $10237万
 $64,024/呎
-(18年-10月-28日)</t>
+(18年-10月)</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -24897,7 +24897,7 @@
           <t>A | 1555呎 (4+房)
 $10006万
 $64,344/呎
-(18年-08月-05日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -24920,7 +24920,7 @@
           <t>A | 1599呎 (4+房)
 $10529万
 $65,846/呎
-(18年-04月-17日)</t>
+(18年-04月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -24943,7 +24943,7 @@
           <t>A | 1599呎 (4+房)
 $9198万
 $57,523/呎
-(18年-06月-20日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24951,7 +24951,7 @@
           <t>B | 1423呎 (4+房)
 $7852万
 $55,181/呎
-(18年-06月-20日)</t>
+(18年-06月)</t>
         </is>
       </c>
     </row>
@@ -24966,7 +24966,7 @@
           <t>A | 1599呎 (4+房)
 $9513万
 $59,493/呎
-(18年-01月-28日)</t>
+(18年-01月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -24974,7 +24974,7 @@
           <t>B | 1467呎 (4+房)
 $8274万
 $56,403/呎
-(18年-01月-29日)</t>
+(18年-01月)</t>
         </is>
       </c>
     </row>
@@ -24989,7 +24989,7 @@
           <t>A | 1599呎 (4+房)
 $950万
 $5,940/呎
-(18年-01月-31日)</t>
+(18年-01月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -24997,7 +24997,7 @@
           <t>B | 1423呎 (4+房)
 $7628万
 $53,608/呎
-(21年-12月-08日)</t>
+(21年-12月)</t>
         </is>
       </c>
     </row>
@@ -25012,7 +25012,7 @@
           <t>A | 1599呎 (4+房)
 $9596万
 $60,010/呎
-(18年-05月-23日)</t>
+(18年-05月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25020,7 +25020,7 @@
           <t>B | 1423呎 (4+房)
 $1429万
 $10,042/呎
-(19年-01月-08日)</t>
+(19年-01月)</t>
         </is>
       </c>
     </row>
@@ -25043,7 +25043,7 @@
           <t>B | 1467呎 (4+房)
 $8000万
 $54,533/呎
-(18年-04月-16日)</t>
+(18年-04月)</t>
         </is>
       </c>
     </row>
@@ -25058,7 +25058,7 @@
           <t>A | 1599呎 (4+房)
 $8319万
 $52,024/呎
-(18年-06月-19日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -25089,7 +25089,7 @@
           <t>B | 1467呎 (4+房)
 $6904万
 $47,061/呎
-(19年-01月-29日)</t>
+(19年-01月)</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
           <t>A | 1599呎 (4+房)
 $7391万
 $46,224/呎
-(18年-07月-04日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -25127,7 +25127,7 @@
           <t>A | 1485呎 (4+房)
 $9848万
 $66,320/呎
-(21年-05月-04日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -25362,7 +25362,7 @@
           <t>A | 1456呎 (4+房)
 $5939万
 $40,789/呎
-(24年-10月-07日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -25592,7 +25592,7 @@
           <t>A | 1456呎 (4+房)
 $7391万
 $50,764/呎
-(18年-06月-10日)</t>
+(18年-06月)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -25773,7 +25773,7 @@
           <t>A | 764呎 (2房)
 $4360万
 $57,075/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
           <t>A | 364呎 (1房)
 $1768万
 $48,582/呎
-(18年-10月-24日)</t>
+(18年-10月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -25822,7 +25822,7 @@
           <t>B | 718呎 (2房)
 $3920万
 $54,596/呎
-(19年-01月-07日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -25831,7 +25831,7 @@
           <t>D | 380呎 (1房)
 $1329万
 $34,977/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -25839,7 +25839,7 @@
           <t>E | 369呎 (1房)
 $1285万
 $34,837/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -25847,7 +25847,7 @@
           <t>F | 286呎 (开放式)
 $1083万
 $37,863/呎
-(18年-08月-05日)</t>
+(18年-08月)</t>
         </is>
       </c>
     </row>
@@ -25862,7 +25862,7 @@
           <t>A | 364呎 (1房)
 $1544万
 $42,407/呎
-(18年-08月-09日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -25870,7 +25870,7 @@
           <t>B | 378呎 (1房)
 $1848万
 $48,893/呎
-(18年-08月-16日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -25878,7 +25878,7 @@
           <t>C | 524呎 (2房)
 $2333万
 $44,527/呎
-(18年-08月-14日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -25886,7 +25886,7 @@
           <t>D | 380呎 (1房)
 $1321万
 $34,751/呎
-(18年-08月-02日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -25894,7 +25894,7 @@
           <t>E | 369呎 (1房)
 $1277万
 $34,612/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -25902,7 +25902,7 @@
           <t>F | 286呎 (开放式)
 $1076万
 $37,620/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
           <t>A | 364呎 (1房)
 $1605万
 $44,087/呎
-(19年-10月-15日)</t>
+(19年-10月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>B | 378呎 (1房)
 $1714万
 $45,343/呎
-(19年-07月-10日)</t>
+(19年-07月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -25933,7 +25933,7 @@
           <t>C | 524呎 (2房)
 $2391万
 $45,629/呎
-(19年-05月-21日)</t>
+(19年-05月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -25941,7 +25941,7 @@
           <t>D | 380呎 (1房)
 $1366万
 $35,938/呎
-(19年-07月-04日)</t>
+(19年-07月)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -25949,7 +25949,7 @@
           <t>E | 369呎 (1房)
 $1341万
 $36,331/呎
-(19年-04月-14日)</t>
+(19年-04月)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -25957,7 +25957,7 @@
           <t>F | 286呎 (开放式)
 $1091万
 $38,146/呎
-(19年-05月-22日)</t>
+(19年-05月)</t>
         </is>
       </c>
     </row>
@@ -25972,7 +25972,7 @@
           <t>A | 364呎 (1房)
 $1528万
 $41,988/呎
-(18年-08月-09日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -25980,7 +25980,7 @@
           <t>B | 378呎 (1房)
 $1656万
 $43,811/呎
-(18年-08月-09日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -25988,7 +25988,7 @@
           <t>C | 524呎 (2房)
 $2310万
 $44,086/呎
-(18年-08月-09日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -25996,7 +25996,7 @@
           <t>D | 380呎 (1房)
 $1339万
 $35,235/呎
-(18年-08月-09日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -26012,7 +26012,7 @@
           <t>F | 286呎 (开放式)
 $1091万
 $38,146/呎
-(20年-07月-14日)</t>
+(20年-07月)</t>
         </is>
       </c>
     </row>
@@ -26035,7 +26035,7 @@
           <t>B | 378呎 (1房)
 $1680万
 $44,456/呎
-(19年-04月-22日)</t>
+(19年-04月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -26043,7 +26043,7 @@
           <t>C | 524呎 (2房)
 $2344万
 $44,735/呎
-(19年-04月-11日)</t>
+(19年-04月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -26051,7 +26051,7 @@
           <t>D | 380呎 (1房)
 $1300万
 $34,203/呎
-(18年-07月-31日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -26059,7 +26059,7 @@
           <t>E | 369呎 (1房)
 $1257万
 $34,066/呎
-(18年-07月-31日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -26082,7 +26082,7 @@
           <t>A | 364呎 (1房)
 $1488万
 $40,878/呎
-(18年-08月-09日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -26090,7 +26090,7 @@
           <t>B | 378呎 (1房)
 $1781万
 $47,129/呎
-(18年-08月-09日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -26098,7 +26098,7 @@
           <t>C | 524呎 (2房)
 $1980万
 $37,786/呎
-(20年-06月-23日)</t>
+(20年-06月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -26106,7 +26106,7 @@
           <t>D | 379呎 (1房)
 $1320万
 $34,821/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -26114,7 +26114,7 @@
           <t>E | 369呎 (1房)
 $1410万
 $38,221/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -26122,7 +26122,7 @@
           <t>F | 286呎 (开放式)
 $1075万
 $37,600/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
     </row>
@@ -26137,7 +26137,7 @@
           <t>A | 364呎 (1房)
 $1551万
 $42,623/呎
-(19年-04月-10日)</t>
+(19年-04月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -26145,7 +26145,7 @@
           <t>B | 378呎 (1房)
 $1657万
 $43,840/呎
-(19年-01月-06日)</t>
+(19年-01月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -26153,7 +26153,7 @@
           <t>C | 524呎 (2房)
 $2312万
 $44,115/呎
-(19年-02月-14日)</t>
+(19年-02月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -26161,7 +26161,7 @@
           <t>D | 379呎 (1房)
 $1424万
 $37,571/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -26169,7 +26169,7 @@
           <t>E | 369呎 (1房)
 $1477万
 $40,031/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -26177,7 +26177,7 @@
           <t>F | 286呎 (开放式)
 $1050万
 $36,713/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -26208,7 +26208,7 @@
           <t>C | 524呎 (2房)
 $2340万
 $44,655/呎
-(21年-11月-17日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -26224,7 +26224,7 @@
           <t>E | 369呎 (1房)
 $1456万
 $39,453/呎
-(20年-07月-02日)</t>
+(20年-07月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -26247,7 +26247,7 @@
           <t>A | 364呎 (1房)
 $1457万
 $40,030/呎
-(18年-07月-30日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -26263,7 +26263,7 @@
           <t>C | 524呎 (2房)
 $2202万
 $42,032/呎
-(18年-09月-02日)</t>
+(18年-09月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -26271,7 +26271,7 @@
           <t>D | 380呎 (1房)
 $1306万
 $34,367/呎
-(18年-08月-08日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -26279,7 +26279,7 @@
           <t>E | 369呎 (1房)
 $1263万
 $34,231/呎
-(18年-08月-13日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -26287,7 +26287,7 @@
           <t>F | 286呎 (开放式)
 $1176万
 $41,110/呎
-(19年-08月-27日)</t>
+(19年-08月)</t>
         </is>
       </c>
     </row>
@@ -26302,7 +26302,7 @@
           <t>A | 364呎 (1房)
 $1447万
 $39,750/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -26310,7 +26310,7 @@
           <t>B | 378呎 (1房)
 $1568万
 $41,479/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -26318,7 +26318,7 @@
           <t>C | 524呎 (2房)
 $2187万
 $41,738/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -26326,7 +26326,7 @@
           <t>D | 380呎 (1房)
 $1277万
 $33,611/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -26334,7 +26334,7 @@
           <t>E | 369呎 (1房)
 $1235万
 $33,476/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -26342,7 +26342,7 @@
           <t>F | 286呎 (开放式)
 $1041万
 $36,385/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
     </row>
@@ -26357,7 +26357,7 @@
           <t>A | 364呎 (1房)
 $1437万
 $39,472/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -26365,7 +26365,7 @@
           <t>B | 378呎 (1房)
 $1557万
 $41,188/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -26373,7 +26373,7 @@
           <t>C | 524呎 (2房)
 $2172万
 $41,446/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -26381,7 +26381,7 @@
           <t>D | 380呎 (1房)
 $1376万
 $36,216/呎
-(18年-08月-07日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -26389,7 +26389,7 @@
           <t>E | 369呎 (1房)
 $1232万
 $33,390/呎
-(18年-08月-12日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -26397,7 +26397,7 @@
           <t>F | 286呎 (开放式)
 $1038万
 $36,294/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -26412,7 +26412,7 @@
           <t>A | 364呎 (1房)
 $1437万
 $39,472/呎
-(18年-08月-05日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -26420,7 +26420,7 @@
           <t>B | 378呎 (1房)
 $1557万
 $41,188/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -26428,7 +26428,7 @@
           <t>C | 524呎 (2房)
 $2172万
 $41,446/呎
-(18年-08月-05日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -26436,7 +26436,7 @@
           <t>D | 380呎 (1房)
 $1408万
 $37,043/呎
-(18年-08月-05日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -26444,7 +26444,7 @@
           <t>E | 369呎 (1房)
 $1232万
 $33,390/呎
-(18年-07月-31日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -26452,7 +26452,7 @@
           <t>F | 286呎 (开放式)
 $1038万
 $36,294/呎
-(18年-08月-06日)</t>
+(18年-08月)</t>
         </is>
       </c>
     </row>
@@ -26467,7 +26467,7 @@
           <t>A | 364呎 (1房)
 $1445万
 $39,699/呎
-(18年-08月-28日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -26475,7 +26475,7 @@
           <t>B | 378呎 (1房)
 $1566万
 $41,424/呎
-(18年-08月-12日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -26483,7 +26483,7 @@
           <t>C | 524呎 (2房)
 $2141万
 $40,865/呎
-(18年-07月-31日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -26491,7 +26491,7 @@
           <t>D | 379呎 (1房)
 $1293万
 $34,116/呎
-(18年-08月-14日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -26499,7 +26499,7 @@
           <t>E | 369呎 (1房)
 $1250万
 $33,888/呎
-(18年-08月-02日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -26507,7 +26507,7 @@
           <t>F | 286呎 (开放式)
 $1053万
 $36,835/呎
-(20年-12月-13日)</t>
+(20年-12月)</t>
         </is>
       </c>
     </row>
@@ -26522,7 +26522,7 @@
           <t>A | 364呎 (1房)
 $1435万
 $39,418/呎
-(18年-08月-28日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26530,7 +26530,7 @@
           <t>B | 378呎 (1房)
 $1680万
 $44,433/呎
-(18年-08月-29日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -26538,7 +26538,7 @@
           <t>C | 524呎 (2房)
 $2169万
 $41,392/呎
-(18年-08月-28日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -26546,7 +26546,7 @@
           <t>D | 380呎 (1房)
 $1290万
 $33,939/呎
-(18年-08月-09日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -26554,7 +26554,7 @@
           <t>E | 369呎 (1房)
 $1285万
 $34,819/呎
-(18年-08月-27日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -26562,7 +26562,7 @@
           <t>F | 286呎 (开放式)
 $1051万
 $36,742/呎
-(19年-05月-16日)</t>
+(19年-05月)</t>
         </is>
       </c>
     </row>
@@ -26577,7 +26577,7 @@
           <t>A | 364呎 (1房)
 $1512万
 $41,541/呎
-(18年-07月-30日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -26585,7 +26585,7 @@
           <t>B | 378呎 (1房)
 $1517万
 $40,125/呎
-(18年-07月-30日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -26593,7 +26593,7 @@
           <t>C | 524呎 (2房)
 $2116万
 $40,378/呎
-(18年-08月-05日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -26601,7 +26601,7 @@
           <t>D | 380呎 (1房)
 $1261万
 $33,191/呎
-(18年-08月-05日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -26609,7 +26609,7 @@
           <t>E | 369呎 (1房)
 $1220万
 $33,059/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -26617,7 +26617,7 @@
           <t>F | 286呎 (开放式)
 $1028万
 $35,934/呎
-(18年-08月-02日)</t>
+(18年-08月)</t>
         </is>
       </c>
     </row>
@@ -26632,7 +26632,7 @@
           <t>A | 364呎 (1房)
 $1393万
 $38,261/呎
-(18年-07月-31日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>B | 378呎 (1房)
 $1509万
 $39,926/呎
-(18年-07月-31日)</t>
+(18年-07月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>C | 524呎 (2房)
 $2105万
 $40,175/呎
-(19年-05月-01日)</t>
+(19年-05月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>D | 380呎 (1房)
 $1258万
 $33,110/呎
-(18年-08月-05日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>E | 369呎 (1房)
 $1217万
 $32,975/呎
-(18年-08月-15日)</t>
+(18年-08月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -26672,7 +26672,7 @@
           <t>F | 286呎 (开放式)
 $1025万
 $35,841/呎
-(18年-07月-29日)</t>
+(18年-07月)</t>
         </is>
       </c>
     </row>
@@ -26922,7 +26922,7 @@
           <t>A | 1559呎 (4+房)
 $8141万
 $52,217/呎
-(25年-09月-03日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -26930,7 +26930,7 @@
           <t>B | 1446呎 (4+房)
 $6827万
 $47,213/呎
-(25年-06月-15日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -26976,7 +26976,7 @@
           <t>B | 1446呎 (4+房)
 $6607万
 $45,690/呎
-(25年-08月-03日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
           <t>A | 1559呎 (4+房)
 $8099万
 $51,950/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -26999,7 +26999,7 @@
           <t>B | 1446呎 (4+房)
 $6496万
 $44,926/呎
-(25年-07月-23日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -27014,7 +27014,7 @@
           <t>A | 1559呎 (4+房)
 $8619万
 $55,284/呎
-(23年-12月-13日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -27022,7 +27022,7 @@
           <t>B | 1446呎 (4+房)
 $6386万
 $44,163/呎
-(25年-06月-16日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -27037,7 +27037,7 @@
           <t>A | 1559呎 (4+房)
 $7209万
 $46,241/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -27045,7 +27045,7 @@
           <t>B | 1446呎 (4+房)
 $6279万
 $43,426/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27060,7 @@
           <t>A | 1559呎 (4+房)
 $7017万
 $45,008/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>B | 1446呎 (4+房)
 $6173万
 $42,690/呎
-(25年-10月-29日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -27083,7 +27083,7 @@
           <t>A | 1559呎 (4+房)
 $6825万
 $43,775/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -27091,7 +27091,7 @@
           <t>B | 1446呎 (4+房)
 $6072万
 $41,990/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -27106,7 +27106,7 @@
           <t>A | 1559呎 (4+房)
 $6632万
 $42,542/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -27129,7 +27129,7 @@
           <t>A | 1559呎 (4+房)
 $6472万
 $41,514/呎
-(25年-08月-07日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">

--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -24439,7 +24439,7 @@
           <t>A | 2031呎 (4+房)
 $15304万
 $75,350/呎
-(20年-01月)</t>
+(20年-01月-21日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -24455,7 +24455,7 @@
           <t>A | 1585呎 (4+房)
 $10355万
 $65,330/呎
-(19年-05月)</t>
+(19年-05月-13日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -24478,7 +24478,7 @@
           <t>A | 1585呎 (4+房)
 $9780万
 $61,703/呎
-(19年-01月)</t>
+(19年-01月-10日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -24486,7 +24486,7 @@
           <t>B | 1173呎 (3房)
 $6745万
 $57,500/呎
-(18年-06月)</t>
+(18年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
           <t>A | 1585呎 (4+房)
 $8927万
 $56,324/呎
-(18年-05月)</t>
+(18年-05月-01日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -24509,7 +24509,7 @@
           <t>B | 1173呎 (3房)
 $6629万
 $56,513/呎
-(18年-06月)</t>
+(18年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -24524,7 +24524,7 @@
           <t>A | 1585呎 (4+房)
 $10285万
 $64,887/呎
-(18年-01月)</t>
+(18年-01月-24日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -24532,7 +24532,7 @@
           <t>B | 1173呎 (3房)
 $7217万
 $61,527/呎
-(18年-01月)</t>
+(18年-01月-24日)</t>
         </is>
       </c>
     </row>
@@ -24547,7 +24547,7 @@
           <t>A | 1585呎 (4+房)
 $8981万
 $56,660/呎
-(18年-01月)</t>
+(18年-01月-09日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24555,7 +24555,7 @@
           <t>B | 1173呎 (3房)
 $6873万
 $58,597/呎
-(18年-01月)</t>
+(18年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -24570,7 +24570,7 @@
           <t>A | 1585呎 (4+房)
 $8876万
 $56,000/呎
-(19年-01月)</t>
+(19年-01月-03日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -24578,7 +24578,7 @@
           <t>B | 1129呎 (3房)
 $6228万
 $55,164/呎
-(19年-08月)</t>
+(19年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -24593,7 +24593,7 @@
           <t>A | 1540呎 (4+房)
 $9935万
 $64,513/呎
-(18年-05月)</t>
+(18年-05月-16日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -24601,7 +24601,7 @@
           <t>B | 1173呎 (3房)
 $6389万
 $54,465/呎
-(18年-04月)</t>
+(18年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
           <t>A | 1540呎 (4+房)
 $8198万
 $53,235/呎
-(18年-06月)</t>
+(18年-06月-05日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -24624,7 +24624,7 @@
           <t>B | 1173呎 (3房)
 $6690万
 $57,033/呎
-(18年-05月)</t>
+(18年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -24647,7 +24647,7 @@
           <t>B | 1173呎 (3房)
 $6104万
 $52,036/呎
-(18年-04月)</t>
+(18年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -24662,7 +24662,7 @@
           <t>A | 1585呎 (4+房)
 $8000万
 $50,473/呎
-(19年-03月)</t>
+(19年-03月-20日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -24670,7 +24670,7 @@
           <t>B | 1173呎 (3房)
 $5706万
 $48,642/呎
-(18年-04月)</t>
+(18年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -24685,7 +24685,7 @@
           <t>A | 1524呎 (4+房)
 $8389万
 $55,045/呎
-(21年-03月)</t>
+(21年-03月-30日)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -24835,7 +24835,7 @@
           <t>A | 2322呎 (4+房)
 $20000万
 $86,133/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -24851,7 +24851,7 @@
           <t>A | 1555呎 (4+房)
 $10900万
 $70,096/呎
-(21年-11月)</t>
+(21年-11月-18日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -24874,7 +24874,7 @@
           <t>A | 1599呎 (4+房)
 $10237万
 $64,024/呎
-(18年-10月)</t>
+(18年-10月-28日)</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -24897,7 +24897,7 @@
           <t>A | 1555呎 (4+房)
 $10006万
 $64,344/呎
-(18年-08月)</t>
+(18年-08月-05日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -24920,7 +24920,7 @@
           <t>A | 1599呎 (4+房)
 $10529万
 $65,846/呎
-(18年-04月)</t>
+(18年-04月-17日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -24943,7 +24943,7 @@
           <t>A | 1599呎 (4+房)
 $9198万
 $57,523/呎
-(18年-06月)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24951,7 +24951,7 @@
           <t>B | 1423呎 (4+房)
 $7852万
 $55,181/呎
-(18年-06月)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -24966,7 +24966,7 @@
           <t>A | 1599呎 (4+房)
 $9513万
 $59,493/呎
-(18年-01月)</t>
+(18年-01月-28日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -24974,7 +24974,7 @@
           <t>B | 1467呎 (4+房)
 $8274万
 $56,403/呎
-(18年-01月)</t>
+(18年-01月-29日)</t>
         </is>
       </c>
     </row>
@@ -24989,7 +24989,7 @@
           <t>A | 1599呎 (4+房)
 $950万
 $5,940/呎
-(18年-01月)</t>
+(18年-01月-31日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -24997,7 +24997,7 @@
           <t>B | 1423呎 (4+房)
 $7628万
 $53,608/呎
-(21年-12月)</t>
+(21年-12月-08日)</t>
         </is>
       </c>
     </row>
@@ -25012,7 +25012,7 @@
           <t>A | 1599呎 (4+房)
 $9596万
 $60,010/呎
-(18年-05月)</t>
+(18年-05月-23日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25020,7 +25020,7 @@
           <t>B | 1423呎 (4+房)
 $1429万
 $10,042/呎
-(19年-01月)</t>
+(19年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -25043,7 +25043,7 @@
           <t>B | 1467呎 (4+房)
 $8000万
 $54,533/呎
-(18年-04月)</t>
+(18年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -25058,7 +25058,7 @@
           <t>A | 1599呎 (4+房)
 $8319万
 $52,024/呎
-(18年-06月)</t>
+(18年-06月-19日)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -25089,7 +25089,7 @@
           <t>B | 1467呎 (4+房)
 $6904万
 $47,061/呎
-(19年-01月)</t>
+(19年-01月-29日)</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
           <t>A | 1599呎 (4+房)
 $7391万
 $46,224/呎
-(18年-07月)</t>
+(18年-07月-04日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -25127,7 +25127,7 @@
           <t>A | 1485呎 (4+房)
 $9848万
 $66,320/呎
-(21年-05月)</t>
+(21年-05月-04日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -25362,7 +25362,7 @@
           <t>A | 1456呎 (4+房)
 $5939万
 $40,789/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -25592,7 +25592,7 @@
           <t>A | 1456呎 (4+房)
 $7391万
 $50,764/呎
-(18年-06月)</t>
+(18年-06月-10日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -25773,7 +25773,7 @@
           <t>A | 764呎 (2房)
 $4360万
 $57,075/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
           <t>A | 364呎 (1房)
 $1768万
 $48,582/呎
-(18年-10月)</t>
+(18年-10月-24日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -25822,7 +25822,7 @@
           <t>B | 718呎 (2房)
 $3920万
 $54,596/呎
-(19年-01月)</t>
+(19年-01月-07日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -25831,7 +25831,7 @@
           <t>D | 380呎 (1房)
 $1329万
 $34,977/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -25839,7 +25839,7 @@
           <t>E | 369呎 (1房)
 $1285万
 $34,837/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -25847,7 +25847,7 @@
           <t>F | 286呎 (开放式)
 $1083万
 $37,863/呎
-(18年-08月)</t>
+(18年-08月-05日)</t>
         </is>
       </c>
     </row>
@@ -25862,7 +25862,7 @@
           <t>A | 364呎 (1房)
 $1544万
 $42,407/呎
-(18年-08月)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -25870,7 +25870,7 @@
           <t>B | 378呎 (1房)
 $1848万
 $48,893/呎
-(18年-08月)</t>
+(18年-08月-16日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -25878,7 +25878,7 @@
           <t>C | 524呎 (2房)
 $2333万
 $44,527/呎
-(18年-08月)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -25886,7 +25886,7 @@
           <t>D | 380呎 (1房)
 $1321万
 $34,751/呎
-(18年-08月)</t>
+(18年-08月-02日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -25894,7 +25894,7 @@
           <t>E | 369呎 (1房)
 $1277万
 $34,612/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -25902,7 +25902,7 @@
           <t>F | 286呎 (开放式)
 $1076万
 $37,620/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
           <t>A | 364呎 (1房)
 $1605万
 $44,087/呎
-(19年-10月)</t>
+(19年-10月-15日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>B | 378呎 (1房)
 $1714万
 $45,343/呎
-(19年-07月)</t>
+(19年-07月-10日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -25933,7 +25933,7 @@
           <t>C | 524呎 (2房)
 $2391万
 $45,629/呎
-(19年-05月)</t>
+(19年-05月-21日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -25941,7 +25941,7 @@
           <t>D | 380呎 (1房)
 $1366万
 $35,938/呎
-(19年-07月)</t>
+(19年-07月-04日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -25949,7 +25949,7 @@
           <t>E | 369呎 (1房)
 $1341万
 $36,331/呎
-(19年-04月)</t>
+(19年-04月-14日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -25957,7 +25957,7 @@
           <t>F | 286呎 (开放式)
 $1091万
 $38,146/呎
-(19年-05月)</t>
+(19年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -25972,7 +25972,7 @@
           <t>A | 364呎 (1房)
 $1528万
 $41,988/呎
-(18年-08月)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -25980,7 +25980,7 @@
           <t>B | 378呎 (1房)
 $1656万
 $43,811/呎
-(18年-08月)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -25988,7 +25988,7 @@
           <t>C | 524呎 (2房)
 $2310万
 $44,086/呎
-(18年-08月)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -25996,7 +25996,7 @@
           <t>D | 380呎 (1房)
 $1339万
 $35,235/呎
-(18年-08月)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -26012,7 +26012,7 @@
           <t>F | 286呎 (开放式)
 $1091万
 $38,146/呎
-(20年-07月)</t>
+(20年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -26035,7 +26035,7 @@
           <t>B | 378呎 (1房)
 $1680万
 $44,456/呎
-(19年-04月)</t>
+(19年-04月-22日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -26043,7 +26043,7 @@
           <t>C | 524呎 (2房)
 $2344万
 $44,735/呎
-(19年-04月)</t>
+(19年-04月-11日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -26051,7 +26051,7 @@
           <t>D | 380呎 (1房)
 $1300万
 $34,203/呎
-(18年-07月)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -26059,7 +26059,7 @@
           <t>E | 369呎 (1房)
 $1257万
 $34,066/呎
-(18年-07月)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -26082,7 +26082,7 @@
           <t>A | 364呎 (1房)
 $1488万
 $40,878/呎
-(18年-08月)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -26090,7 +26090,7 @@
           <t>B | 378呎 (1房)
 $1781万
 $47,129/呎
-(18年-08月)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -26098,7 +26098,7 @@
           <t>C | 524呎 (2房)
 $1980万
 $37,786/呎
-(20年-06月)</t>
+(20年-06月-23日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -26106,7 +26106,7 @@
           <t>D | 379呎 (1房)
 $1320万
 $34,821/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -26114,7 +26114,7 @@
           <t>E | 369呎 (1房)
 $1410万
 $38,221/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -26122,7 +26122,7 @@
           <t>F | 286呎 (开放式)
 $1075万
 $37,600/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -26137,7 +26137,7 @@
           <t>A | 364呎 (1房)
 $1551万
 $42,623/呎
-(19年-04月)</t>
+(19年-04月-10日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -26145,7 +26145,7 @@
           <t>B | 378呎 (1房)
 $1657万
 $43,840/呎
-(19年-01月)</t>
+(19年-01月-06日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -26153,7 +26153,7 @@
           <t>C | 524呎 (2房)
 $2312万
 $44,115/呎
-(19年-02月)</t>
+(19年-02月-14日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -26161,7 +26161,7 @@
           <t>D | 379呎 (1房)
 $1424万
 $37,571/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -26169,7 +26169,7 @@
           <t>E | 369呎 (1房)
 $1477万
 $40,031/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -26177,7 +26177,7 @@
           <t>F | 286呎 (开放式)
 $1050万
 $36,713/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -26208,7 +26208,7 @@
           <t>C | 524呎 (2房)
 $2340万
 $44,655/呎
-(21年-11月)</t>
+(21年-11月-17日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -26224,7 +26224,7 @@
           <t>E | 369呎 (1房)
 $1456万
 $39,453/呎
-(20年-07月)</t>
+(20年-07月-02日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -26247,7 +26247,7 @@
           <t>A | 364呎 (1房)
 $1457万
 $40,030/呎
-(18年-07月)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -26263,7 +26263,7 @@
           <t>C | 524呎 (2房)
 $2202万
 $42,032/呎
-(18年-09月)</t>
+(18年-09月-02日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -26271,7 +26271,7 @@
           <t>D | 380呎 (1房)
 $1306万
 $34,367/呎
-(18年-08月)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -26279,7 +26279,7 @@
           <t>E | 369呎 (1房)
 $1263万
 $34,231/呎
-(18年-08月)</t>
+(18年-08月-13日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -26287,7 +26287,7 @@
           <t>F | 286呎 (开放式)
 $1176万
 $41,110/呎
-(19年-08月)</t>
+(19年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -26302,7 +26302,7 @@
           <t>A | 364呎 (1房)
 $1447万
 $39,750/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -26310,7 +26310,7 @@
           <t>B | 378呎 (1房)
 $1568万
 $41,479/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -26318,7 +26318,7 @@
           <t>C | 524呎 (2房)
 $2187万
 $41,738/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -26326,7 +26326,7 @@
           <t>D | 380呎 (1房)
 $1277万
 $33,611/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -26334,7 +26334,7 @@
           <t>E | 369呎 (1房)
 $1235万
 $33,476/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -26342,7 +26342,7 @@
           <t>F | 286呎 (开放式)
 $1041万
 $36,385/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -26357,7 +26357,7 @@
           <t>A | 364呎 (1房)
 $1437万
 $39,472/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -26365,7 +26365,7 @@
           <t>B | 378呎 (1房)
 $1557万
 $41,188/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -26373,7 +26373,7 @@
           <t>C | 524呎 (2房)
 $2172万
 $41,446/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -26381,7 +26381,7 @@
           <t>D | 380呎 (1房)
 $1376万
 $36,216/呎
-(18年-08月)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -26389,7 +26389,7 @@
           <t>E | 369呎 (1房)
 $1232万
 $33,390/呎
-(18年-08月)</t>
+(18年-08月-12日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -26397,7 +26397,7 @@
           <t>F | 286呎 (开放式)
 $1038万
 $36,294/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -26412,7 +26412,7 @@
           <t>A | 364呎 (1房)
 $1437万
 $39,472/呎
-(18年-08月)</t>
+(18年-08月-05日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -26420,7 +26420,7 @@
           <t>B | 378呎 (1房)
 $1557万
 $41,188/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -26428,7 +26428,7 @@
           <t>C | 524呎 (2房)
 $2172万
 $41,446/呎
-(18年-08月)</t>
+(18年-08月-05日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -26436,7 +26436,7 @@
           <t>D | 380呎 (1房)
 $1408万
 $37,043/呎
-(18年-08月)</t>
+(18年-08月-05日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -26444,7 +26444,7 @@
           <t>E | 369呎 (1房)
 $1232万
 $33,390/呎
-(18年-07月)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -26452,7 +26452,7 @@
           <t>F | 286呎 (开放式)
 $1038万
 $36,294/呎
-(18年-08月)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -26467,7 +26467,7 @@
           <t>A | 364呎 (1房)
 $1445万
 $39,699/呎
-(18年-08月)</t>
+(18年-08月-28日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -26475,7 +26475,7 @@
           <t>B | 378呎 (1房)
 $1566万
 $41,424/呎
-(18年-08月)</t>
+(18年-08月-12日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -26483,7 +26483,7 @@
           <t>C | 524呎 (2房)
 $2141万
 $40,865/呎
-(18年-07月)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -26491,7 +26491,7 @@
           <t>D | 379呎 (1房)
 $1293万
 $34,116/呎
-(18年-08月)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -26499,7 +26499,7 @@
           <t>E | 369呎 (1房)
 $1250万
 $33,888/呎
-(18年-08月)</t>
+(18年-08月-02日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -26507,7 +26507,7 @@
           <t>F | 286呎 (开放式)
 $1053万
 $36,835/呎
-(20年-12月)</t>
+(20年-12月-13日)</t>
         </is>
       </c>
     </row>
@@ -26522,7 +26522,7 @@
           <t>A | 364呎 (1房)
 $1435万
 $39,418/呎
-(18年-08月)</t>
+(18年-08月-28日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26530,7 +26530,7 @@
           <t>B | 378呎 (1房)
 $1680万
 $44,433/呎
-(18年-08月)</t>
+(18年-08月-29日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -26538,7 +26538,7 @@
           <t>C | 524呎 (2房)
 $2169万
 $41,392/呎
-(18年-08月)</t>
+(18年-08月-28日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -26546,7 +26546,7 @@
           <t>D | 380呎 (1房)
 $1290万
 $33,939/呎
-(18年-08月)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -26554,7 +26554,7 @@
           <t>E | 369呎 (1房)
 $1285万
 $34,819/呎
-(18年-08月)</t>
+(18年-08月-27日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -26562,7 +26562,7 @@
           <t>F | 286呎 (开放式)
 $1051万
 $36,742/呎
-(19年-05月)</t>
+(19年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -26577,7 +26577,7 @@
           <t>A | 364呎 (1房)
 $1512万
 $41,541/呎
-(18年-07月)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -26585,7 +26585,7 @@
           <t>B | 378呎 (1房)
 $1517万
 $40,125/呎
-(18年-07月)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -26593,7 +26593,7 @@
           <t>C | 524呎 (2房)
 $2116万
 $40,378/呎
-(18年-08月)</t>
+(18年-08月-05日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -26601,7 +26601,7 @@
           <t>D | 380呎 (1房)
 $1261万
 $33,191/呎
-(18年-08月)</t>
+(18年-08月-05日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -26609,7 +26609,7 @@
           <t>E | 369呎 (1房)
 $1220万
 $33,059/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -26617,7 +26617,7 @@
           <t>F | 286呎 (开放式)
 $1028万
 $35,934/呎
-(18年-08月)</t>
+(18年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -26632,7 +26632,7 @@
           <t>A | 364呎 (1房)
 $1393万
 $38,261/呎
-(18年-07月)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>B | 378呎 (1房)
 $1509万
 $39,926/呎
-(18年-07月)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>C | 524呎 (2房)
 $2105万
 $40,175/呎
-(19年-05月)</t>
+(19年-05月-01日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>D | 380呎 (1房)
 $1258万
 $33,110/呎
-(18年-08月)</t>
+(18年-08月-05日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>E | 369呎 (1房)
 $1217万
 $32,975/呎
-(18年-08月)</t>
+(18年-08月-15日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -26672,7 +26672,7 @@
           <t>F | 286呎 (开放式)
 $1025万
 $35,841/呎
-(18年-07月)</t>
+(18年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -26922,7 +26922,7 @@
           <t>A | 1559呎 (4+房)
 $8141万
 $52,217/呎
-(25年-09月)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -26930,7 +26930,7 @@
           <t>B | 1446呎 (4+房)
 $6827万
 $47,213/呎
-(25年-06月)</t>
+(25年-06月-15日)</t>
         </is>
       </c>
     </row>
@@ -26976,7 +26976,7 @@
           <t>B | 1446呎 (4+房)
 $6607万
 $45,690/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
           <t>A | 1559呎 (4+房)
 $8099万
 $51,950/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -26999,7 +26999,7 @@
           <t>B | 1446呎 (4+房)
 $6496万
 $44,926/呎
-(25年-07月)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
     </row>
@@ -27014,7 +27014,7 @@
           <t>A | 1559呎 (4+房)
 $8619万
 $55,284/呎
-(23年-12月)</t>
+(23年-12月-13日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -27022,7 +27022,7 @@
           <t>B | 1446呎 (4+房)
 $6386万
 $44,163/呎
-(25年-06月)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -27037,7 +27037,7 @@
           <t>A | 1559呎 (4+房)
 $7209万
 $46,241/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -27045,7 +27045,7 @@
           <t>B | 1446呎 (4+房)
 $6279万
 $43,426/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27060,7 @@
           <t>A | 1559呎 (4+房)
 $7017万
 $45,008/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>B | 1446呎 (4+房)
 $6173万
 $42,690/呎
-(25年-10月)</t>
+(25年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -27083,7 +27083,7 @@
           <t>A | 1559呎 (4+房)
 $6825万
 $43,775/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -27091,7 +27091,7 @@
           <t>B | 1446呎 (4+房)
 $6072万
 $41,990/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -27106,7 +27106,7 @@
           <t>A | 1559呎 (4+房)
 $6632万
 $42,542/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -27129,7 +27129,7 @@
           <t>A | 1559呎 (4+房)
 $6472万
 $41,514/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
